--- a/pm/route-days-v2/Spine-Route-Days-Sean.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Sean.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Passed in W1/W2 — revisit rotation</t>
+          <t>Passed in cycle 1 (Jul 22–31) — revisit rotation</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3579,7 +3579,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3639,7 +3639,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3729,7 +3729,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3759,7 +3759,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3819,7 +3819,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/pm/route-days-v2/Spine-Route-Days-Sean.xlsx
+++ b/pm/route-days-v2/Spine-Route-Days-Sean.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -101,6 +106,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3496,21 +3507,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="72" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cycle 2 plan. First pass = the full day. Cadence revisit / Producer sweep = the producing accounts only (2–4 quick stops). Pick the weekday at the Monday huddle.</t>
+          <t>5 route-day slots per week. First pass = the full day. Cadence revisit = the producers due on rhythm, packed into one full loop day (a label like R03+R07 = one drive covering both days’ producers). Open slots are flex. Pick weekdays at the Monday huddle.</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3538,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Route Day</t>
+          <t>Route Day(s)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3547,49 +3558,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>S-R01</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Cadence revisit</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Open slot ×2</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>S-R02</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>S-R01</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -3598,28 +3607,28 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
+          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>S-R03</t>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>S-R02</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3628,28 +3637,28 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Michigan Primary Care - Sterling Heights · Associates in Family Practice · Schoenherr Parkway Family Practice · Macomb Internal Medicine</t>
+          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>S-R04</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>S-R01+R02+R04</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3658,28 +3667,28 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
+          <t>Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Wattles Internal Medicine- use · Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>S-R01</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>S-R03</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3688,28 +3697,28 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights</t>
+          <t>Michigan Primary Care - Sterling Heights · Associates in Family Practice · Schoenherr Parkway Family Practice · Macomb Internal Medicine</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>S-R01</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>S-R03</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -3722,24 +3731,24 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine</t>
+          <t>Toma &amp; Yaldo Medical Center · Sterling Heights Urgent Care · David S Weingarden MD &amp; Associates · Office of David Mandy DO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>S-R03</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>S-R04</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -3748,26 +3757,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Michigan Primary Care - Sterling Heights · Associates in Family Practice · Schoenherr Parkway Family Practice · Macomb Internal Medicine</t>
+          <t>MyCare Health Center - Mt Clemens · Masonic Medical Center - Ascension · Aquino Integrative Internal Medicine · Epic Health - St Clair Shores · Waypointe Internal Medicine · Allied Internists · Roseville Family Practice · Sterling Medical Center &amp; Urgent Care</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>S-R01</t>
         </is>
@@ -3789,17 +3798,17 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>S-R03</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>S-R02</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3808,41 +3817,247 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Beaumont Family Medicine - Sterling Heights · Academic Internal Medicine (Ascension)</t>
+          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>S-R03+R04</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Cadence revisit</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson · Michigan Primary Care - Sterling Heights · Associates in Family Practice · Schoenherr Parkway Family Practice · Macomb Internal Medicine · Beaumont Family Medicine - Sterling Heights · Academic Internal Medicine (Ascension)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Open slot ×1</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>S-R01+R02</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Cadence revisit</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Horizon Care Medical Group - Warren · Get Well Urgent Care - Warren · Pioneer Medical Associates - Warren · Michigan Adult and Child Medicine · South Lyon Family Docs · Downriver Internists · Elite Family Medicine · Wattles Internal Medicine- use</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Open slot ×1</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Flex: backlog pull-forward · huddle promotes · ortho field day</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>S-R01+R03</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Cadence revisit</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Ryan Medical Associates · Michigan Compassionate Care · DIAB AND KINNER INTERNAL MEDICINE, PC- use · MI Family Practice · Get Well Urgent Care - Sterling Heights · Toma &amp; Yaldo Medical Center · Sterling Heights Urgent Care · David S Weingarden MD &amp; Associates · Office of David Mandy DO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>S-R02</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cadence revisit</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Berkley Urgent Care · Get Well Urgent Care Madison Heights · Kashat Urgent care · Sterling Physicians · Tri-County Medical Clinic · Brigid Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>S-R03</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Cadence revisit</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Michigan Primary Care - Sterling Heights · Associates in Family Practice · Schoenherr Parkway Family Practice · Macomb Internal Medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>S-R04</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Cadence revisit</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson</t>
+      <c r="E19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Cornerstone Lakefront Internists · Henry Ford Medical Center - East Jefferson · MyCare Health Center - Mt Clemens · Masonic Medical Center - Ascension · Aquino Integrative Internal Medicine · Epic Health - St Clair Shores · Waypointe Internal Medicine · Allied Internists · Roseville Family Practice · Sterling Medical Center &amp; Urgent Care</t>
         </is>
       </c>
     </row>
